--- a/docs/GovHub_SaaS_Metrics_v2.xlsx
+++ b/docs/GovHub_SaaS_Metrics_v2.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="697">
   <si>
     <t xml:space="preserve">GOVHUB — SAAS METRICS &amp; PROJECTIONS WORKBOOK  (v2, rebuilt on real data)</t>
   </si>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">Cost stack — provided directly by the founder, 2026-08-13. Marked as such on the Expenses tab.</t>
   </si>
   <si>
-    <t xml:space="preserve">TWO OPEN ITEMS YOU NEED TO RESOLVE</t>
+    <t xml:space="preserve">THE OPEN ITEM YOU NEED TO RESOLVE</t>
   </si>
   <si>
     <t xml:space="preserve">1. Stripe is not wired up. Every row in the plans table has a null stripe_price_id (monthly and annual). There is no</t>
@@ -140,10 +140,7 @@
     <t xml:space="preserve">   code path that can take money today. Until that ships, trial → paid conversion is structurally 0%, not behaviourally 0%.</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Supabase is not in your cost list. The GovProp project is ACTIVE_HEALTHY and serving production. If it is on the free</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   tier, it is a capacity risk; if it is billed, it is a missing cost line. Expenses row is stubbed at $0 pending your answer.</t>
+    <t xml:space="preserve">   (Supabase was resolved 2026-08-13: $25.00/month, now booked on the Expenses tab.)</t>
   </si>
   <si>
     <t xml:space="preserve">EXECUTIVE DASHBOARD — as of 2026-08-13</t>
@@ -1481,13 +1478,10 @@
     <t xml:space="preserve">Supabase</t>
   </si>
   <si>
-    <t xml:space="preserve">unknown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OPEN ITEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOT in the founder's cost list, but GovProp is ACTIVE_HEALTHY in production. Confirm tier.</t>
+    <t xml:space="preserve">$25.00 / month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Founder-provided. Hosts the GovProp production database.</t>
   </si>
   <si>
     <t xml:space="preserve">Subtotal — Operational</t>
@@ -2126,7 +2120,7 @@
     <t xml:space="preserve">≥12 months</t>
   </si>
   <si>
-    <t xml:space="preserve">At ~$413/mo burn this is governed by your personal runway, not the company's.</t>
+    <t xml:space="preserve">At ~$419/mo burn this is governed by your personal runway, not the company's.</t>
   </si>
 </sst>
 </file>
@@ -2872,7 +2866,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -3079,11 +3073,6 @@
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="4" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="4" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -3116,7 +3105,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3147,7 +3136,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3178,12 +3167,12 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -3214,7 +3203,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B7" s="67" t="n">
         <f aca="false">Calculator!B18</f>
@@ -3223,7 +3212,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B8" s="37" t="n">
         <v>0.15</v>
@@ -3231,7 +3220,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B9" s="68" t="n">
         <f aca="false">Calculator!B19</f>
@@ -3240,7 +3229,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B10" s="65" t="n">
         <f aca="false">Calculator!B20</f>
@@ -3249,7 +3238,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B11" s="65" t="n">
         <f aca="false">Calculator!B21</f>
@@ -3258,7 +3247,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B12" s="67" t="n">
         <f aca="false">Calculator!B30</f>
@@ -3267,7 +3256,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B13" s="37" t="n">
         <v>0.05</v>
@@ -3275,7 +3264,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B14" s="68" t="n">
         <f aca="false">IFERROR(Calculator!B42/Calculator!B30,0)</f>
@@ -3284,7 +3273,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B15" s="57" t="n">
         <f aca="false">Calculator!B47</f>
@@ -3293,7 +3282,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B16" s="43" t="n">
         <f aca="false">Calculator!B15</f>
@@ -3302,7 +3291,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B17" s="65" t="n">
         <f aca="false">Calculator!B50</f>
@@ -3311,7 +3300,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B18" s="65" t="n">
         <f aca="false">Calculator!B51</f>
@@ -3320,7 +3309,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B19" s="65" t="n">
         <f aca="false">Calculator!B52</f>
@@ -3329,16 +3318,16 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B20" s="69" t="n">
         <f aca="false">Expenses!C22+Calculator!B56</f>
-        <v>5393.98333333333</v>
+        <v>5418.98333333333</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B21" s="37" t="n">
         <v>0.02</v>
@@ -3346,7 +3335,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -3377,85 +3366,85 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="32" t="s">
+        <v>575</v>
+      </c>
+      <c r="D24" s="32" t="s">
+        <v>576</v>
+      </c>
+      <c r="E24" s="32" t="s">
         <v>577</v>
       </c>
-      <c r="D24" s="32" t="s">
+      <c r="F24" s="32" t="s">
         <v>578</v>
       </c>
-      <c r="E24" s="32" t="s">
+      <c r="G24" s="32" t="s">
         <v>579</v>
       </c>
-      <c r="F24" s="32" t="s">
+      <c r="H24" s="32" t="s">
         <v>580</v>
       </c>
-      <c r="G24" s="32" t="s">
+      <c r="I24" s="32" t="s">
         <v>581</v>
       </c>
-      <c r="H24" s="32" t="s">
+      <c r="J24" s="32" t="s">
         <v>582</v>
       </c>
-      <c r="I24" s="32" t="s">
+      <c r="K24" s="32" t="s">
         <v>583</v>
       </c>
-      <c r="J24" s="32" t="s">
+      <c r="L24" s="32" t="s">
         <v>584</v>
       </c>
-      <c r="K24" s="32" t="s">
+      <c r="M24" s="32" t="s">
         <v>585</v>
       </c>
-      <c r="L24" s="32" t="s">
+      <c r="N24" s="32" t="s">
         <v>586</v>
       </c>
-      <c r="M24" s="32" t="s">
+      <c r="O24" s="32" t="s">
         <v>587</v>
       </c>
-      <c r="N24" s="32" t="s">
+      <c r="P24" s="32" t="s">
         <v>588</v>
       </c>
-      <c r="O24" s="32" t="s">
+      <c r="Q24" s="32" t="s">
         <v>589</v>
       </c>
-      <c r="P24" s="32" t="s">
+      <c r="R24" s="32" t="s">
         <v>590</v>
       </c>
-      <c r="Q24" s="32" t="s">
+      <c r="S24" s="32" t="s">
         <v>591</v>
       </c>
-      <c r="R24" s="32" t="s">
+      <c r="T24" s="32" t="s">
         <v>592</v>
       </c>
-      <c r="S24" s="32" t="s">
+      <c r="U24" s="32" t="s">
         <v>593</v>
       </c>
-      <c r="T24" s="32" t="s">
+      <c r="V24" s="32" t="s">
         <v>594</v>
       </c>
-      <c r="U24" s="32" t="s">
+      <c r="W24" s="32" t="s">
         <v>595</v>
       </c>
-      <c r="V24" s="32" t="s">
+      <c r="X24" s="32" t="s">
         <v>596</v>
       </c>
-      <c r="W24" s="32" t="s">
+      <c r="Y24" s="32" t="s">
         <v>597</v>
       </c>
-      <c r="X24" s="32" t="s">
+      <c r="Z24" s="32" t="s">
         <v>598</v>
-      </c>
-      <c r="Y24" s="32" t="s">
-        <v>599</v>
-      </c>
-      <c r="Z24" s="32" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="34" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C25" s="14" t="n">
         <f aca="false">$B$7</f>
@@ -3556,7 +3545,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="34" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C26" s="40" t="n">
         <f aca="false">C25*$B$9</f>
@@ -3657,7 +3646,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="34" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C27" s="40" t="n">
         <f aca="false">C26*$B$10</f>
@@ -3758,7 +3747,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="34" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C28" s="40" t="n">
         <f aca="false">C27*$B$11</f>
@@ -3859,7 +3848,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="34" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C29" s="14" t="n">
         <f aca="false">$B$12</f>
@@ -3960,7 +3949,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="34" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C30" s="40" t="n">
         <f aca="false">C29*$B$14</f>
@@ -4061,7 +4050,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="34" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C31" s="40" t="n">
         <f aca="false">$B$15</f>
@@ -4162,7 +4151,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C32" s="40" t="n">
         <f aca="false">C28+C30+C31</f>
@@ -4263,7 +4252,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="34" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C34" s="40" t="n">
         <f aca="false">0</f>
@@ -4364,7 +4353,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="34" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C35" s="40" t="n">
         <f aca="false">C34*$B$17</f>
@@ -4465,7 +4454,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C36" s="40" t="n">
         <f aca="false">C34+C32-C35</f>
@@ -4566,7 +4555,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="34" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C38" s="11" t="n">
         <f aca="false">0</f>
@@ -4667,7 +4656,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="34" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C39" s="11" t="n">
         <f aca="false">C32*$B$16</f>
@@ -4768,7 +4757,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="34" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C40" s="11" t="n">
         <f aca="false">C38*$B$18</f>
@@ -4869,7 +4858,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="34" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C41" s="11" t="n">
         <f aca="false">C38*$B$17</f>
@@ -4970,7 +4959,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="34" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C42" s="11" t="n">
         <f aca="false">C39+C40-C41</f>
@@ -5071,7 +5060,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C43" s="11" t="n">
         <f aca="false">C38+C42</f>
@@ -5172,7 +5161,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="34" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C44" s="11" t="n">
         <f aca="false">C43*12</f>
@@ -5273,7 +5262,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="34" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C46" s="11" t="n">
         <f aca="false">C43*$B$19</f>
@@ -5374,209 +5363,209 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="34" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C47" s="11" t="n">
         <f aca="false">$B$20</f>
-        <v>5393.98333333333</v>
+        <v>5418.98333333333</v>
       </c>
       <c r="D47" s="11" t="n">
         <f aca="false">C47*(1+$B$21)</f>
-        <v>5501.863</v>
+        <v>5527.363</v>
       </c>
       <c r="E47" s="11" t="n">
         <f aca="false">D47*(1+$B$21)</f>
-        <v>5611.90026</v>
+        <v>5637.91026</v>
       </c>
       <c r="F47" s="11" t="n">
         <f aca="false">E47*(1+$B$21)</f>
-        <v>5724.1382652</v>
+        <v>5750.6684652</v>
       </c>
       <c r="G47" s="11" t="n">
         <f aca="false">F47*(1+$B$21)</f>
-        <v>5838.621030504</v>
+        <v>5865.681834504</v>
       </c>
       <c r="H47" s="11" t="n">
         <f aca="false">G47*(1+$B$21)</f>
-        <v>5955.39345111408</v>
+        <v>5982.99547119408</v>
       </c>
       <c r="I47" s="11" t="n">
         <f aca="false">H47*(1+$B$21)</f>
-        <v>6074.50132013636</v>
+        <v>6102.65538061796</v>
       </c>
       <c r="J47" s="11" t="n">
         <f aca="false">I47*(1+$B$21)</f>
-        <v>6195.99134653909</v>
+        <v>6224.70848823032</v>
       </c>
       <c r="K47" s="11" t="n">
         <f aca="false">J47*(1+$B$21)</f>
-        <v>6319.91117346987</v>
+        <v>6349.20265799493</v>
       </c>
       <c r="L47" s="11" t="n">
         <f aca="false">K47*(1+$B$21)</f>
-        <v>6446.30939693927</v>
+        <v>6476.18671115483</v>
       </c>
       <c r="M47" s="11" t="n">
         <f aca="false">L47*(1+$B$21)</f>
-        <v>6575.23558487806</v>
+        <v>6605.71044537792</v>
       </c>
       <c r="N47" s="11" t="n">
         <f aca="false">M47*(1+$B$21)</f>
-        <v>6706.74029657562</v>
+        <v>6737.82465428548</v>
       </c>
       <c r="O47" s="11" t="n">
         <f aca="false">N47*(1+$B$21)</f>
-        <v>6840.87510250713</v>
+        <v>6872.58114737119</v>
       </c>
       <c r="P47" s="11" t="n">
         <f aca="false">O47*(1+$B$21)</f>
-        <v>6977.69260455727</v>
+        <v>7010.03277031862</v>
       </c>
       <c r="Q47" s="11" t="n">
         <f aca="false">P47*(1+$B$21)</f>
-        <v>7117.24645664842</v>
+        <v>7150.23342572499</v>
       </c>
       <c r="R47" s="11" t="n">
         <f aca="false">Q47*(1+$B$21)</f>
-        <v>7259.59138578139</v>
+        <v>7293.23809423949</v>
       </c>
       <c r="S47" s="11" t="n">
         <f aca="false">R47*(1+$B$21)</f>
-        <v>7404.78321349702</v>
+        <v>7439.10285612428</v>
       </c>
       <c r="T47" s="11" t="n">
         <f aca="false">S47*(1+$B$21)</f>
-        <v>7552.87887776696</v>
+        <v>7587.88491324676</v>
       </c>
       <c r="U47" s="11" t="n">
         <f aca="false">T47*(1+$B$21)</f>
-        <v>7703.93645532229</v>
+        <v>7739.6426115117</v>
       </c>
       <c r="V47" s="11" t="n">
         <f aca="false">U47*(1+$B$21)</f>
-        <v>7858.01518442874</v>
+        <v>7894.43546374193</v>
       </c>
       <c r="W47" s="11" t="n">
         <f aca="false">V47*(1+$B$21)</f>
-        <v>8015.17548811732</v>
+        <v>8052.32417301677</v>
       </c>
       <c r="X47" s="11" t="n">
         <f aca="false">W47*(1+$B$21)</f>
-        <v>8175.47899787966</v>
+        <v>8213.37065647711</v>
       </c>
       <c r="Y47" s="11" t="n">
         <f aca="false">X47*(1+$B$21)</f>
-        <v>8338.98857783726</v>
+        <v>8377.63806960665</v>
       </c>
       <c r="Z47" s="11" t="n">
         <f aca="false">Y47*(1+$B$21)</f>
-        <v>8505.768349394</v>
+        <v>8545.19083099878</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C48" s="11" t="n">
         <f aca="false">C46-C47</f>
-        <v>-4558.10919310083</v>
+        <v>-4583.10919310083</v>
       </c>
       <c r="D48" s="11" t="n">
         <f aca="false">D46-D47</f>
-        <v>-3825.05539896121</v>
+        <v>-3850.55539896121</v>
       </c>
       <c r="E48" s="11" t="n">
         <f aca="false">E46-E47</f>
-        <v>-3087.11754817548</v>
+        <v>-3113.12754817548</v>
       </c>
       <c r="F48" s="11" t="n">
         <f aca="false">F46-F47</f>
-        <v>-2342.28752308152</v>
+        <v>-2368.81772308152</v>
       </c>
       <c r="G48" s="11" t="n">
         <f aca="false">G46-G47</f>
-        <v>-1588.47862514316</v>
+        <v>-1615.53942914316</v>
       </c>
       <c r="H48" s="11" t="n">
         <f aca="false">H46-H47</f>
-        <v>-823.5139680454</v>
+        <v>-851.115988125399</v>
       </c>
       <c r="I48" s="11" t="n">
         <f aca="false">I46-I47</f>
-        <v>-45.1135869271484</v>
+        <v>-73.2676474087475</v>
       </c>
       <c r="J48" s="11" t="n">
         <f aca="false">J46-J47</f>
-        <v>749.119923693578</v>
+        <v>720.402782002347</v>
       </c>
       <c r="K48" s="11" t="n">
         <f aca="false">K46-K47</f>
-        <v>1561.71745789434</v>
+        <v>1532.42597336928</v>
       </c>
       <c r="L48" s="11" t="n">
         <f aca="false">L46-L47</f>
-        <v>2395.36137801417</v>
+        <v>2365.48406379861</v>
       </c>
       <c r="M48" s="11" t="n">
         <f aca="false">M46-M47</f>
-        <v>3252.90570765876</v>
+        <v>3222.43084715889</v>
       </c>
       <c r="N48" s="11" t="n">
         <f aca="false">N46-N47</f>
-        <v>4137.39886090393</v>
+        <v>4106.31450319407</v>
       </c>
       <c r="O48" s="11" t="n">
         <f aca="false">O46-O47</f>
-        <v>5052.10927792207</v>
+        <v>5020.403233058</v>
       </c>
       <c r="P48" s="11" t="n">
         <f aca="false">P46-P47</f>
-        <v>6000.55439169804</v>
+        <v>5968.2142259367</v>
       </c>
       <c r="Q48" s="11" t="n">
         <f aca="false">Q46-Q47</f>
-        <v>6986.53341307771</v>
+        <v>6953.54644400114</v>
       </c>
       <c r="R48" s="11" t="n">
         <f aca="false">R46-R47</f>
-        <v>8014.16449332093</v>
+        <v>7980.51778486283</v>
       </c>
       <c r="S48" s="11" t="n">
         <f aca="false">S46-S47</f>
-        <v>9087.92690601333</v>
+        <v>9053.60726338607</v>
       </c>
       <c r="T48" s="11" t="n">
         <f aca="false">T46-T47</f>
-        <v>10212.7089852359</v>
+        <v>10177.7029497561</v>
       </c>
       <c r="U48" s="11" t="n">
         <f aca="false">U46-U47</f>
-        <v>11393.8626661512</v>
+        <v>11358.1565099618</v>
       </c>
       <c r="V48" s="11" t="n">
         <f aca="false">V46-V47</f>
-        <v>12637.2655997698</v>
+        <v>12600.8453204566</v>
       </c>
       <c r="W48" s="11" t="n">
         <f aca="false">W46-W47</f>
-        <v>13949.3919580554</v>
+        <v>13912.243273156</v>
       </c>
       <c r="X48" s="11" t="n">
         <f aca="false">X46-X47</f>
-        <v>15337.3932115349</v>
+        <v>15299.5015529375</v>
       </c>
       <c r="Y48" s="11" t="n">
         <f aca="false">Y46-Y47</f>
-        <v>16809.1903524292</v>
+        <v>16770.5408606598</v>
       </c>
       <c r="Z48" s="11" t="n">
         <f aca="false">Z46-Z47</f>
-        <v>18373.5792557433</v>
+        <v>18334.1567741386</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
@@ -5607,7 +5596,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B52" s="38" t="n">
         <f aca="false">N43</f>
@@ -5616,7 +5605,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B53" s="38" t="n">
         <f aca="false">Z43</f>
@@ -5625,7 +5614,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B54" s="38" t="n">
         <f aca="false">Z44</f>
@@ -5634,7 +5623,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B55" s="42" t="n">
         <f aca="false">Z36</f>
@@ -5643,7 +5632,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B56" s="70" t="n">
         <f aca="false">Calculator!B70</f>
@@ -5652,7 +5641,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B57" s="71" t="str">
         <f aca="false">IFERROR(INDEX($C$24:$Z$24,MATCH(TRUE(),INDEX($C$48:$Z$48&gt;0,0),0)),"not within 24 months")</f>
@@ -5661,7 +5650,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B58" s="72" t="n">
         <f aca="false">COUNTIF(C48:Z48,"&gt;0")</f>
@@ -5670,12 +5659,12 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="23" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
   </sheetData>
@@ -5713,7 +5702,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5722,7 +5711,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5731,352 +5720,352 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>625</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="D5" s="7" t="s">
         <v>626</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>627</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>629</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>630</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
+        <v>630</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>632</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="D7" s="7" t="s">
         <v>633</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>634</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>636</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>637</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>639</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>640</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
+        <v>640</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>642</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>643</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>649</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>650</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>652</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
+        <v>653</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>655</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="D15" s="7" t="s">
         <v>656</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>657</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>659</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>660</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
+        <v>661</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>663</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="D18" s="7" t="s">
         <v>664</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>665</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>667</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>668</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>670</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>671</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>673</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>674</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>676</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>677</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>679</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>680</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>682</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>683</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>685</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>686</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
+        <v>686</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>688</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="D26" s="7" t="s">
         <v>689</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>690</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>692</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>693</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
+        <v>693</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>695</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="D28" s="7" t="s">
         <v>696</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>697</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>698</v>
       </c>
     </row>
   </sheetData>
@@ -6112,7 +6101,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6123,7 +6112,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6134,7 +6123,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -6145,30 +6134,30 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="C5" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="D5" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="G5" s="9" t="s">
         <v>46</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B6" s="10" t="n">
         <f aca="false">Revenue!O25</f>
@@ -6183,18 +6172,18 @@
         <v>0</v>
       </c>
       <c r="E6" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="G6" s="7" t="s">
         <v>50</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B7" s="13" t="n">
         <f aca="false">Revenue!O16</f>
@@ -6209,18 +6198,18 @@
         <v>0</v>
       </c>
       <c r="E7" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>53</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B8" s="10" t="n">
         <f aca="false">B6*12</f>
@@ -6235,70 +6224,70 @@
         <v>0</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B9" s="13" t="n">
         <f aca="false">Funnel!C10</f>
         <v>30</v>
       </c>
       <c r="E9" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="G9" s="7" t="s">
         <v>59</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="13" t="n">
         <f aca="false">Funnel!C11</f>
         <v>9</v>
       </c>
       <c r="E10" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>62</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B11" s="13" t="n">
         <f aca="false">Funnel!B30</f>
         <v>3</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -6309,30 +6298,30 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B14" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="D14" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="9" t="s">
+      <c r="F14" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="9" t="s">
         <v>69</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B15" s="13" t="n">
         <f aca="false">SEO!O6</f>
@@ -6347,18 +6336,18 @@
         <v>113</v>
       </c>
       <c r="E15" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F15" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="G15" s="7" t="s">
         <v>73</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B16" s="13" t="n">
         <f aca="false">SEO!O7</f>
@@ -6373,36 +6362,36 @@
         <v>20</v>
       </c>
       <c r="E16" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="G16" s="7" t="s">
         <v>77</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B17" s="13" t="n">
         <f aca="false">Funnel!C13</f>
         <v>30</v>
       </c>
       <c r="E17" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G17" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="F17" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B18" s="17" t="n">
         <f aca="false">Expenses!N40</f>
@@ -6417,36 +6406,36 @@
         <v>-18.85</v>
       </c>
       <c r="E18" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="F18" s="16" t="s">
+      <c r="G18" s="7" t="s">
         <v>84</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B19" s="13" t="n">
         <f aca="false">'Cold Email'!O8</f>
         <v>0</v>
       </c>
       <c r="E19" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F19" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="F19" s="19" t="s">
+      <c r="G19" s="7" t="s">
         <v>88</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -6457,126 +6446,126 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F22" s="9"/>
       <c r="G22" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" s="20" t="s">
         <v>93</v>
-      </c>
-      <c r="B23" s="20" t="s">
-        <v>94</v>
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="20"/>
       <c r="E23" s="21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F23" s="21"/>
       <c r="G23" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C24" s="20"/>
       <c r="D24" s="20"/>
       <c r="E24" s="21" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F24" s="21"/>
       <c r="G24" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C25" s="20"/>
       <c r="D25" s="20"/>
       <c r="E25" s="21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F25" s="21"/>
       <c r="G25" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="20"/>
       <c r="E26" s="21" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F26" s="21"/>
       <c r="G26" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="20"/>
       <c r="E27" s="21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F27" s="21"/>
       <c r="G27" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C28" s="20"/>
       <c r="D28" s="20"/>
       <c r="E28" s="21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F28" s="21"/>
       <c r="G28" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -6587,10 +6576,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B31" s="22" t="s">
         <v>112</v>
-      </c>
-      <c r="B31" s="22" t="s">
-        <v>113</v>
       </c>
       <c r="C31" s="22"/>
       <c r="D31" s="22"/>
@@ -6600,10 +6589,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B32" s="22" t="s">
         <v>114</v>
-      </c>
-      <c r="B32" s="22" t="s">
-        <v>115</v>
       </c>
       <c r="C32" s="22"/>
       <c r="D32" s="22"/>
@@ -6613,10 +6602,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" s="22" t="s">
         <v>116</v>
-      </c>
-      <c r="B33" s="22" t="s">
-        <v>117</v>
       </c>
       <c r="C33" s="22"/>
       <c r="D33" s="22"/>
@@ -6673,7 +6662,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6686,7 +6675,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6699,12 +6688,12 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -6717,52 +6706,52 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="C7" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="D7" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="E7" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="F7" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="24" t="s">
         <v>126</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="G7" s="24" t="s">
-        <v>127</v>
       </c>
       <c r="H7" s="24"/>
       <c r="I7" s="24"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>128</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>129</v>
       </c>
       <c r="C8" s="25"/>
       <c r="E8" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H8" s="21"/>
       <c r="I8" s="21"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>131</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>132</v>
       </c>
       <c r="C9" s="26" t="n">
         <v>41</v>
@@ -6772,20 +6761,20 @@
         <v/>
       </c>
       <c r="E9" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G9" s="21" t="s">
         <v>133</v>
-      </c>
-      <c r="G9" s="21" t="s">
-        <v>134</v>
       </c>
       <c r="H9" s="21"/>
       <c r="I9" s="21"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>135</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>136</v>
       </c>
       <c r="C10" s="26" t="n">
         <v>30</v>
@@ -6795,39 +6784,39 @@
         <v>0.731707317073171</v>
       </c>
       <c r="E10" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="G10" s="21" t="s">
         <v>137</v>
-      </c>
-      <c r="G10" s="21" t="s">
-        <v>138</v>
       </c>
       <c r="H10" s="21"/>
       <c r="I10" s="21"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>139</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>140</v>
       </c>
       <c r="C11" s="26" t="n">
         <v>9</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H11" s="21"/>
       <c r="I11" s="21"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>142</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>143</v>
       </c>
       <c r="C12" s="26" t="n">
         <v>21</v>
@@ -6837,39 +6826,39 @@
         <v>0.7</v>
       </c>
       <c r="E12" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="G12" s="21" t="s">
         <v>144</v>
-      </c>
-      <c r="G12" s="21" t="s">
-        <v>145</v>
       </c>
       <c r="H12" s="21"/>
       <c r="I12" s="21"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>146</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>147</v>
       </c>
       <c r="C13" s="26" t="n">
         <v>30</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H13" s="21"/>
       <c r="I13" s="21"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>149</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>150</v>
       </c>
       <c r="C14" s="26" t="n">
         <v>0</v>
@@ -6879,24 +6868,24 @@
         <v>0</v>
       </c>
       <c r="E14" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G14" s="21" t="s">
         <v>151</v>
-      </c>
-      <c r="G14" s="21" t="s">
-        <v>152</v>
       </c>
       <c r="H14" s="21"/>
       <c r="I14" s="21"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D16" s="27" t="n">
         <f aca="false">IFERROR(C14/C9,0)</f>
         <v>0</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F16" s="20"/>
       <c r="G16" s="20"/>
@@ -6905,7 +6894,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -6918,39 +6907,39 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="B19" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" s="9" t="s">
+      <c r="D19" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="E19" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="F19" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="H19" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="F19" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="H19" s="9" t="s">
+      <c r="I19" s="9" t="s">
         <v>160</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B20" s="16" t="s">
         <v>162</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>163</v>
       </c>
       <c r="C20" s="26"/>
       <c r="D20" s="26" t="n">
@@ -6970,15 +6959,15 @@
         <v>0</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B21" s="19" t="s">
         <v>165</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>166</v>
       </c>
       <c r="C21" s="26" t="n">
         <v>0</v>
@@ -7000,15 +6989,15 @@
         <v>0</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B22" s="15" t="s">
         <v>168</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>169</v>
       </c>
       <c r="C22" s="26" t="n">
         <v>48</v>
@@ -7030,15 +7019,15 @@
         <v>0</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C23" s="26" t="n">
         <v>0</v>
@@ -7060,12 +7049,12 @@
         <v>0</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C24" s="29" t="n">
         <f aca="false">SUM(C20:C23)</f>
@@ -7094,7 +7083,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -7107,22 +7096,22 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D27" s="9"/>
       <c r="E27" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B28" s="26" t="n">
         <v>29</v>
@@ -7132,7 +7121,7 @@
         <v>1</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F28" s="21"/>
       <c r="G28" s="21"/>
@@ -7141,7 +7130,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B29" s="26" t="n">
         <v>26</v>
@@ -7151,7 +7140,7 @@
         <v>0.896551724137931</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F29" s="21"/>
       <c r="G29" s="21"/>
@@ -7160,7 +7149,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B30" s="26" t="n">
         <v>3</v>
@@ -7170,7 +7159,7 @@
         <v>0.103448275862069</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F30" s="21"/>
       <c r="G30" s="21"/>
@@ -7179,7 +7168,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B31" s="26" t="n">
         <v>0</v>
@@ -7189,7 +7178,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F31" s="21"/>
       <c r="G31" s="21"/>
@@ -7198,7 +7187,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -7211,57 +7200,57 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C34" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="D34" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="D34" s="32" t="s">
+      <c r="E34" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="E34" s="32" t="s">
+      <c r="F34" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="F34" s="32" t="s">
+      <c r="G34" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="G34" s="32" t="s">
+      <c r="H34" s="32" t="s">
         <v>189</v>
       </c>
-      <c r="H34" s="32" t="s">
+      <c r="I34" s="32" t="s">
         <v>190</v>
       </c>
-      <c r="I34" s="32" t="s">
+      <c r="J34" s="32" t="s">
         <v>191</v>
       </c>
-      <c r="J34" s="32" t="s">
+      <c r="K34" s="32" t="s">
         <v>192</v>
       </c>
-      <c r="K34" s="32" t="s">
+      <c r="L34" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="L34" s="32" t="s">
+      <c r="M34" s="32" t="s">
         <v>194</v>
       </c>
-      <c r="M34" s="32" t="s">
+      <c r="N34" s="32" t="s">
         <v>195</v>
       </c>
-      <c r="N34" s="32" t="s">
+      <c r="O34" s="32" t="s">
         <v>196</v>
-      </c>
-      <c r="O34" s="32" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B35" s="23" t="s">
         <v>198</v>
-      </c>
-      <c r="B35" s="23" t="s">
-        <v>199</v>
       </c>
       <c r="C35" s="33" t="n">
         <v>1</v>
@@ -7306,10 +7295,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B36" s="23" t="s">
         <v>200</v>
-      </c>
-      <c r="B36" s="23" t="s">
-        <v>201</v>
       </c>
       <c r="C36" s="33" t="n">
         <v>1</v>
@@ -7354,10 +7343,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="B37" s="23" t="s">
         <v>202</v>
-      </c>
-      <c r="B37" s="23" t="s">
-        <v>203</v>
       </c>
       <c r="C37" s="33" t="n">
         <v>0</v>
@@ -7402,10 +7391,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B38" s="23" t="s">
         <v>204</v>
-      </c>
-      <c r="B38" s="23" t="s">
-        <v>205</v>
       </c>
       <c r="C38" s="33" t="n">
         <v>1</v>
@@ -7450,10 +7439,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="34" t="s">
+        <v>205</v>
+      </c>
+      <c r="B39" s="23" t="s">
         <v>206</v>
-      </c>
-      <c r="B39" s="23" t="s">
-        <v>207</v>
       </c>
       <c r="C39" s="31" t="n">
         <f aca="false">IFERROR(C38/C35,"")</f>
@@ -7510,10 +7499,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B40" s="23" t="s">
         <v>208</v>
-      </c>
-      <c r="B40" s="23" t="s">
-        <v>209</v>
       </c>
       <c r="C40" s="33" t="n">
         <v>0</v>
@@ -7558,10 +7547,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B41" s="23" t="s">
         <v>210</v>
-      </c>
-      <c r="B41" s="23" t="s">
-        <v>211</v>
       </c>
       <c r="C41" s="33" t="n">
         <v>0</v>
@@ -7606,10 +7595,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B42" s="23" t="s">
         <v>212</v>
-      </c>
-      <c r="B42" s="23" t="s">
-        <v>213</v>
       </c>
       <c r="C42" s="33" t="n">
         <v>0</v>
@@ -7701,7 +7690,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7715,7 +7704,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -7729,7 +7718,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -7743,51 +7732,51 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B5" s="36" t="n">
         <v>129</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B6" s="36" t="n">
         <v>349</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B7" s="36" t="n">
         <v>699</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B8" s="37" t="n">
         <v>0.6</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B9" s="37" t="n">
         <v>0.32</v>
@@ -7795,7 +7784,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B10" s="37" t="n">
         <v>0.08</v>
@@ -7803,7 +7792,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B11" s="31" t="n">
         <f aca="false">B8+B9+B10</f>
@@ -7816,53 +7805,53 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B12" s="38" t="n">
         <f aca="false">B5*B8+B6*B9+B7*B10</f>
         <v>245</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B13" s="37" t="n">
         <v>0.2</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B14" s="39" t="n">
         <v>0.1667</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B15" s="38" t="n">
         <f aca="false">B12*(1-B13*B14)</f>
         <v>236.8317</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
@@ -7876,51 +7865,51 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B18" s="25" t="n">
         <v>41</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B19" s="37" t="n">
         <v>0.025</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B20" s="37" t="n">
         <v>0.7</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B21" s="37" t="n">
         <v>0.12</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="34" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B22" s="40" t="n">
         <f aca="false">B18*B19</f>
@@ -7929,7 +7918,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="34" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B23" s="40" t="n">
         <f aca="false">B22*B20</f>
@@ -7938,7 +7927,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="41" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B24" s="42" t="n">
         <f aca="false">B23*B21</f>
@@ -7947,7 +7936,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -7961,40 +7950,40 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B27" s="25" t="n">
         <v>12</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B28" s="25" t="n">
         <v>15</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B29" s="25" t="n">
         <v>22</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="34" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B30" s="14" t="n">
         <f aca="false">B27*B28*B29</f>
@@ -8003,18 +7992,18 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B31" s="37" t="n">
         <v>0.02</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="34" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B32" s="14" t="n">
         <f aca="false">B30*(1-B31)</f>
@@ -8023,29 +8012,29 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B33" s="37" t="n">
         <v>0.034</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B34" s="37" t="n">
         <v>0.33</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B35" s="37" t="n">
         <v>0.42</v>
@@ -8053,7 +8042,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B36" s="37" t="n">
         <v>0.65</v>
@@ -8061,18 +8050,18 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B37" s="37" t="n">
         <v>0.3</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="34" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B38" s="40" t="n">
         <f aca="false">B32*B33</f>
@@ -8081,7 +8070,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="34" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B39" s="40" t="n">
         <f aca="false">B38*B34</f>
@@ -8090,7 +8079,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="34" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B40" s="40" t="n">
         <f aca="false">B39*B35</f>
@@ -8099,7 +8088,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B41" s="40" t="n">
         <f aca="false">B40*B36</f>
@@ -8108,7 +8097,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="41" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B42" s="42" t="n">
         <f aca="false">B41*B37</f>
@@ -8117,7 +8106,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -8131,29 +8120,29 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B45" s="25" t="n">
         <v>2</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B46" s="37" t="n">
         <v>0.25</v>
       </c>
       <c r="C46" s="23" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="41" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B47" s="42" t="n">
         <f aca="false">B45*B46</f>
@@ -8162,7 +8151,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -8176,88 +8165,88 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B50" s="37" t="n">
         <v>0.05</v>
       </c>
       <c r="C50" s="23" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B51" s="37" t="n">
         <v>0.01</v>
       </c>
       <c r="C51" s="23" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B52" s="37" t="n">
         <v>0.85</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B53" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="23" t="s">
         <v>283</v>
-      </c>
-      <c r="B53" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" s="23" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B54" s="43" t="n">
         <f aca="false">Expenses!C20</f>
         <v>257.75</v>
       </c>
       <c r="C54" s="23" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B55" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="23" t="s">
         <v>287</v>
-      </c>
-      <c r="B55" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C55" s="23" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B56" s="36" t="n">
         <v>5000</v>
       </c>
       <c r="C56" s="23" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B57" s="44" t="s">
         <v>291</v>
-      </c>
-      <c r="B57" s="44" t="s">
-        <v>292</v>
       </c>
       <c r="C57" s="44"/>
       <c r="D57" s="44"/>
@@ -8269,7 +8258,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
@@ -8283,254 +8272,254 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B60" s="9" t="s">
         <v>41</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>42</v>
       </c>
       <c r="C60" s="9"/>
       <c r="D60" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E60" s="9"/>
       <c r="F60" s="9"/>
       <c r="G60" s="9"/>
       <c r="H60" s="9"/>
       <c r="I60" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B61" s="42" t="n">
         <f aca="false">B24+B42+B47</f>
         <v>4.1522369744</v>
       </c>
       <c r="D61" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E61" s="21"/>
       <c r="F61" s="21"/>
       <c r="G61" s="21"/>
       <c r="H61" s="21"/>
       <c r="I61" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B62" s="38" t="n">
         <f aca="false">B61*B15</f>
         <v>983.381341450008</v>
       </c>
       <c r="D62" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E62" s="21"/>
       <c r="F62" s="21"/>
       <c r="G62" s="21"/>
       <c r="H62" s="21"/>
       <c r="I62" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B63" s="38" t="n">
         <f aca="false">B53+B54+B55+B56</f>
         <v>5257.75</v>
       </c>
       <c r="D63" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E63" s="21"/>
       <c r="F63" s="21"/>
       <c r="G63" s="21"/>
       <c r="H63" s="21"/>
       <c r="I63" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B64" s="38" t="n">
         <f aca="false">IFERROR(B63/B61,0)</f>
         <v>1266.24516674166</v>
       </c>
       <c r="D64" s="21" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E64" s="21"/>
       <c r="F64" s="21"/>
       <c r="G64" s="21"/>
       <c r="H64" s="21"/>
       <c r="I64" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B65" s="38" t="n">
         <f aca="false">IFERROR(B53/B24,0)</f>
         <v>0</v>
       </c>
       <c r="D65" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E65" s="21"/>
       <c r="F65" s="21"/>
       <c r="G65" s="21"/>
       <c r="H65" s="21"/>
       <c r="I65" s="7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B66" s="38" t="n">
         <f aca="false">IFERROR(B54/B42,0)</f>
         <v>72.2770891444421</v>
       </c>
       <c r="D66" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E66" s="21"/>
       <c r="F66" s="21"/>
       <c r="G66" s="21"/>
       <c r="H66" s="21"/>
       <c r="I66" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B67" s="38" t="n">
         <f aca="false">IFERROR(B15*B52/B50,0)</f>
         <v>4026.1389</v>
       </c>
       <c r="D67" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E67" s="21"/>
       <c r="F67" s="21"/>
       <c r="G67" s="21"/>
       <c r="H67" s="21"/>
       <c r="I67" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B68" s="45" t="n">
         <f aca="false">IFERROR(B67/B64,0)</f>
         <v>3.17958876033477</v>
       </c>
       <c r="D68" s="21" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E68" s="21"/>
       <c r="F68" s="21"/>
       <c r="G68" s="21"/>
       <c r="H68" s="21"/>
       <c r="I68" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B69" s="42" t="n">
         <f aca="false">IFERROR(B64/(B15*B52),0)</f>
         <v>6.29012161871344</v>
       </c>
       <c r="D69" s="21" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E69" s="21"/>
       <c r="F69" s="21"/>
       <c r="G69" s="21"/>
       <c r="H69" s="21"/>
       <c r="I69" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B70" s="38" t="n">
         <f aca="false">IFERROR(B62/B50,0)</f>
         <v>19667.6268290002</v>
       </c>
       <c r="D70" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E70" s="21"/>
       <c r="F70" s="21"/>
       <c r="G70" s="21"/>
       <c r="H70" s="21"/>
       <c r="I70" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B71" s="42" t="n">
         <f aca="false">IF(B70&lt;=10000,"never",LN(1-10000*B50/B62)/LN(1-B50))</f>
         <v>13.845691153503</v>
       </c>
       <c r="D71" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E71" s="21"/>
       <c r="F71" s="21"/>
       <c r="G71" s="21"/>
       <c r="H71" s="21"/>
       <c r="I71" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B72" s="42" t="n">
         <f aca="false">IF(B70*B52&lt;=(Expenses!$C$22+B56),"never",LN(1-((Expenses!$C$22+B56)/B52)*B50/B62)/LN(1-B50))</f>
-        <v>7.59504503340277</v>
+        <v>7.63813524336233</v>
       </c>
       <c r="D72" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E72" s="21"/>
       <c r="F72" s="21"/>
       <c r="G72" s="21"/>
       <c r="H72" s="21"/>
       <c r="I72" s="7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B74" s="8"/>
       <c r="C74" s="8"/>
@@ -8544,12 +8533,12 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="23" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B77" s="46" t="n">
         <v>150</v>
@@ -8694,12 +8683,12 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="23" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B85" s="46" t="n">
         <v>150</v>
@@ -8844,12 +8833,12 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="23" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B93" s="49" t="n">
         <v>5</v>
@@ -8994,12 +8983,12 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="23" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B101" s="46" t="n">
         <v>150</v>
@@ -9144,7 +9133,7 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="23" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -9197,7 +9186,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -9217,7 +9206,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -9237,12 +9226,12 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -9262,51 +9251,51 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="23" t="s">
         <v>336</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>339</v>
-      </c>
       <c r="C8" s="51" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>341</v>
-      </c>
       <c r="C9" s="51" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>343</v>
-      </c>
       <c r="C10" s="51" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -9326,57 +9315,57 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C13" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="D13" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="E13" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="E13" s="32" t="s">
+      <c r="F13" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="F13" s="32" t="s">
+      <c r="G13" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="H13" s="32" t="s">
         <v>189</v>
       </c>
-      <c r="H13" s="32" t="s">
+      <c r="I13" s="32" t="s">
         <v>190</v>
       </c>
-      <c r="I13" s="32" t="s">
+      <c r="J13" s="32" t="s">
         <v>191</v>
       </c>
-      <c r="J13" s="32" t="s">
+      <c r="K13" s="32" t="s">
         <v>192</v>
       </c>
-      <c r="K13" s="32" t="s">
+      <c r="L13" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="L13" s="32" t="s">
+      <c r="M13" s="32" t="s">
         <v>194</v>
       </c>
-      <c r="M13" s="32" t="s">
+      <c r="N13" s="32" t="s">
         <v>195</v>
       </c>
-      <c r="N13" s="32" t="s">
+      <c r="O13" s="32" t="s">
         <v>196</v>
-      </c>
-      <c r="O13" s="32" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="B14" s="23" t="s">
         <v>345</v>
-      </c>
-      <c r="B14" s="23" t="s">
-        <v>346</v>
       </c>
       <c r="C14" s="33" t="n">
         <v>0</v>
@@ -9421,10 +9410,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C15" s="33" t="n">
         <v>0</v>
@@ -9469,10 +9458,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="B16" s="23" t="s">
         <v>348</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>349</v>
       </c>
       <c r="C16" s="33" t="n">
         <v>0</v>
@@ -9517,7 +9506,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -9537,7 +9526,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B19" s="23"/>
       <c r="C19" s="52" t="n">
@@ -9583,10 +9572,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="B20" s="23" t="s">
         <v>352</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>353</v>
       </c>
       <c r="C20" s="52" t="n">
         <v>0</v>
@@ -9631,10 +9620,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C21" s="52" t="n">
         <v>0</v>
@@ -9679,10 +9668,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C22" s="52" t="n">
         <v>0</v>
@@ -9727,10 +9716,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C23" s="52" t="n">
         <v>0</v>
@@ -9775,7 +9764,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B24" s="23"/>
       <c r="C24" s="52" t="n">
@@ -9821,7 +9810,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B25" s="23"/>
       <c r="C25" s="52" t="n">
@@ -9867,10 +9856,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C26" s="52" t="n">
         <v>0</v>
@@ -9915,7 +9904,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="23" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -9951,7 +9940,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -9971,7 +9960,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -9991,7 +9980,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -10011,57 +10000,57 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C5" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="D5" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="E5" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="F5" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="G5" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="G5" s="32" t="s">
+      <c r="H5" s="32" t="s">
         <v>189</v>
       </c>
-      <c r="H5" s="32" t="s">
+      <c r="I5" s="32" t="s">
         <v>190</v>
       </c>
-      <c r="I5" s="32" t="s">
+      <c r="J5" s="32" t="s">
         <v>191</v>
       </c>
-      <c r="J5" s="32" t="s">
+      <c r="K5" s="32" t="s">
         <v>192</v>
       </c>
-      <c r="K5" s="32" t="s">
+      <c r="L5" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="L5" s="32" t="s">
+      <c r="M5" s="32" t="s">
         <v>194</v>
       </c>
-      <c r="M5" s="32" t="s">
+      <c r="N5" s="32" t="s">
         <v>195</v>
       </c>
-      <c r="N5" s="32" t="s">
+      <c r="O5" s="32" t="s">
         <v>196</v>
-      </c>
-      <c r="O5" s="32" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="B6" s="23" t="s">
         <v>364</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>365</v>
       </c>
       <c r="C6" s="33" t="n">
         <v>0</v>
@@ -10106,10 +10095,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="B7" s="23" t="s">
         <v>366</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>367</v>
       </c>
       <c r="C7" s="33" t="n">
         <v>0</v>
@@ -10154,10 +10143,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="B8" s="23" t="s">
         <v>368</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>369</v>
       </c>
       <c r="C8" s="33" t="n">
         <v>0</v>
@@ -10200,10 +10189,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="B9" s="23" t="s">
         <v>370</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>371</v>
       </c>
       <c r="C9" s="52" t="n">
         <v>0</v>
@@ -10248,12 +10237,12 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -10273,27 +10262,27 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>374</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="C14" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="D14" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="E14" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="F14" s="9" t="s">
         <v>378</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B15" s="33" t="n">
         <v>23</v>
@@ -10308,12 +10297,12 @@
         <v>0.7</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B16" s="33" t="n">
         <v>7</v>
@@ -10328,12 +10317,12 @@
         <v>0.05</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B17" s="33" t="n">
         <v>14</v>
@@ -10348,12 +10337,12 @@
         <v>0.05</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B18" s="33" t="n">
         <v>29</v>
@@ -10368,12 +10357,12 @@
         <v>0</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B19" s="33" t="n">
         <v>19</v>
@@ -10388,12 +10377,12 @@
         <v>0</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B20" s="33" t="n">
         <v>31</v>
@@ -10408,12 +10397,12 @@
         <v>0</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B21" s="33" t="n">
         <v>40</v>
@@ -10428,12 +10417,12 @@
         <v>0</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B22" s="33" t="n">
         <v>58</v>
@@ -10448,12 +10437,12 @@
         <v>0</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B23" s="33" t="n">
         <v>70</v>
@@ -10468,12 +10457,12 @@
         <v>0</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B24" s="33" t="n">
         <v>71</v>
@@ -10488,22 +10477,22 @@
         <v>0</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="51" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -10523,57 +10512,57 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C30" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="D30" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="D30" s="32" t="s">
+      <c r="E30" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="E30" s="32" t="s">
+      <c r="F30" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="F30" s="32" t="s">
+      <c r="G30" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="G30" s="32" t="s">
+      <c r="H30" s="32" t="s">
         <v>189</v>
       </c>
-      <c r="H30" s="32" t="s">
+      <c r="I30" s="32" t="s">
         <v>190</v>
       </c>
-      <c r="I30" s="32" t="s">
+      <c r="J30" s="32" t="s">
         <v>191</v>
       </c>
-      <c r="J30" s="32" t="s">
+      <c r="K30" s="32" t="s">
         <v>192</v>
       </c>
-      <c r="K30" s="32" t="s">
+      <c r="L30" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="L30" s="32" t="s">
+      <c r="M30" s="32" t="s">
         <v>194</v>
       </c>
-      <c r="M30" s="32" t="s">
+      <c r="N30" s="32" t="s">
         <v>195</v>
       </c>
-      <c r="N30" s="32" t="s">
+      <c r="O30" s="32" t="s">
         <v>196</v>
-      </c>
-      <c r="O30" s="32" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="B31" s="23" t="s">
         <v>402</v>
-      </c>
-      <c r="B31" s="23" t="s">
-        <v>403</v>
       </c>
       <c r="C31" s="33" t="n">
         <v>0</v>
@@ -10618,10 +10607,10 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C32" s="33" t="n">
         <v>0</v>
@@ -10666,10 +10655,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="B33" s="23" t="s">
         <v>405</v>
-      </c>
-      <c r="B33" s="23" t="s">
-        <v>406</v>
       </c>
       <c r="C33" s="52" t="n">
         <v>0</v>
@@ -10714,10 +10703,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="34" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C34" s="27" t="str">
         <f aca="false">IFERROR(C31/C7,"")</f>
@@ -10805,7 +10794,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10825,7 +10814,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -10845,12 +10834,12 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -10870,57 +10859,57 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C7" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="D7" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="E7" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="F7" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="F7" s="32" t="s">
+      <c r="G7" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="G7" s="32" t="s">
+      <c r="H7" s="32" t="s">
         <v>189</v>
       </c>
-      <c r="H7" s="32" t="s">
+      <c r="I7" s="32" t="s">
         <v>190</v>
       </c>
-      <c r="I7" s="32" t="s">
+      <c r="J7" s="32" t="s">
         <v>191</v>
       </c>
-      <c r="J7" s="32" t="s">
+      <c r="K7" s="32" t="s">
         <v>192</v>
       </c>
-      <c r="K7" s="32" t="s">
+      <c r="L7" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="L7" s="32" t="s">
+      <c r="M7" s="32" t="s">
         <v>194</v>
       </c>
-      <c r="M7" s="32" t="s">
+      <c r="N7" s="32" t="s">
         <v>195</v>
       </c>
-      <c r="N7" s="32" t="s">
+      <c r="O7" s="32" t="s">
         <v>196</v>
-      </c>
-      <c r="O7" s="32" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C8" s="33" t="n">
         <v>0</v>
@@ -10965,10 +10954,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="B9" s="23" t="s">
         <v>413</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>414</v>
       </c>
       <c r="C9" s="33" t="n">
         <v>0</v>
@@ -11013,10 +11002,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C10" s="33" t="n">
         <v>0</v>
@@ -11061,10 +11050,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C11" s="33" t="n">
         <v>0</v>
@@ -11109,10 +11098,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="B12" s="23" t="s">
         <v>417</v>
-      </c>
-      <c r="B12" s="23" t="s">
-        <v>418</v>
       </c>
       <c r="C12" s="33" t="n">
         <v>0</v>
@@ -11157,10 +11146,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="B13" s="23" t="s">
         <v>419</v>
-      </c>
-      <c r="B13" s="23" t="s">
-        <v>420</v>
       </c>
       <c r="C13" s="33" t="n">
         <v>0</v>
@@ -11205,7 +11194,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -11225,57 +11214,57 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C16" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="D16" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="E16" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="F16" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="F16" s="32" t="s">
+      <c r="G16" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="G16" s="32" t="s">
+      <c r="H16" s="32" t="s">
         <v>189</v>
       </c>
-      <c r="H16" s="32" t="s">
+      <c r="I16" s="32" t="s">
         <v>190</v>
       </c>
-      <c r="I16" s="32" t="s">
+      <c r="J16" s="32" t="s">
         <v>191</v>
       </c>
-      <c r="J16" s="32" t="s">
+      <c r="K16" s="32" t="s">
         <v>192</v>
       </c>
-      <c r="K16" s="32" t="s">
+      <c r="L16" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="L16" s="32" t="s">
+      <c r="M16" s="32" t="s">
         <v>194</v>
       </c>
-      <c r="M16" s="32" t="s">
+      <c r="N16" s="32" t="s">
         <v>195</v>
       </c>
-      <c r="N16" s="32" t="s">
+      <c r="O16" s="32" t="s">
         <v>196</v>
-      </c>
-      <c r="O16" s="32" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="B17" s="23" t="s">
         <v>422</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>423</v>
       </c>
       <c r="C17" s="33" t="n">
         <v>0</v>
@@ -11320,12 +11309,12 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="23" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -11345,84 +11334,84 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="B22" s="9" t="s">
         <v>426</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="C22" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="B23" s="56" t="s">
         <v>428</v>
       </c>
-      <c r="B23" s="56" t="s">
+      <c r="C23" s="7" t="s">
         <v>429</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="B24" s="56" t="s">
         <v>431</v>
       </c>
-      <c r="B24" s="56" t="s">
+      <c r="C24" s="7" t="s">
         <v>432</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="B25" s="56" t="s">
         <v>434</v>
       </c>
-      <c r="B25" s="56" t="s">
+      <c r="C25" s="7" t="s">
         <v>435</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="B26" s="56" t="s">
         <v>437</v>
       </c>
-      <c r="B26" s="56" t="s">
+      <c r="C26" s="7" t="s">
         <v>438</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="B27" s="56" t="s">
         <v>440</v>
       </c>
-      <c r="B27" s="56" t="s">
+      <c r="C27" s="7" t="s">
         <v>441</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="B28" s="56" t="s">
         <v>443</v>
       </c>
-      <c r="B28" s="56" t="s">
+      <c r="C28" s="7" t="s">
         <v>444</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -11442,23 +11431,23 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="23" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B32" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="C32" s="9" t="s">
         <v>448</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B33" s="57" t="n">
         <f aca="false">Calculator!B30</f>
@@ -11471,7 +11460,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B34" s="57" t="n">
         <f aca="false">Calculator!B32</f>
@@ -11484,7 +11473,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B35" s="57" t="n">
         <f aca="false">Calculator!B38</f>
@@ -11497,7 +11486,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B36" s="57" t="n">
         <f aca="false">Calculator!B39</f>
@@ -11510,7 +11499,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B37" s="57" t="n">
         <f aca="false">Calculator!B40</f>
@@ -11523,7 +11512,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B38" s="57" t="n">
         <f aca="false">Calculator!B41</f>
@@ -11536,7 +11525,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B39" s="57" t="n">
         <f aca="false">Calculator!B42</f>
@@ -11571,7 +11560,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P50"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
@@ -11581,7 +11570,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11601,7 +11590,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11621,7 +11610,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -11632,33 +11621,33 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>458</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="C5" s="9" t="s">
         <v>459</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="D5" s="9" t="s">
         <v>460</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="E5" s="9" t="s">
         <v>461</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>462</v>
-      </c>
       <c r="F5" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>463</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>464</v>
       </c>
       <c r="C6" s="58" t="n">
         <v>100</v>
@@ -11668,21 +11657,21 @@
         <v>1200</v>
       </c>
       <c r="E6" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>465</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="G6" s="7" t="s">
         <v>466</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>468</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>469</v>
       </c>
       <c r="C7" s="17" t="n">
         <f aca="false">N40</f>
@@ -11693,21 +11682,21 @@
         <v>94.8</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F7" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>470</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C8" s="58" t="n">
         <v>0</v>
@@ -11717,21 +11706,21 @@
         <v>0</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>474</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>475</v>
       </c>
       <c r="C9" s="58" t="n">
         <v>20</v>
@@ -11741,21 +11730,21 @@
         <v>240</v>
       </c>
       <c r="E9" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>465</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="G9" s="7" t="s">
         <v>466</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>476</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>477</v>
       </c>
       <c r="C10" s="58" t="n">
         <v>5</v>
@@ -11765,21 +11754,21 @@
         <v>60</v>
       </c>
       <c r="E10" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>465</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="G10" s="7" t="s">
         <v>466</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>478</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>479</v>
       </c>
       <c r="C11" s="18" t="n">
         <f aca="false">D11/12</f>
@@ -11789,58 +11778,58 @@
         <v>40</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F11" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>480</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="C12" s="58" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D12" s="18" t="n">
         <f aca="false">C12*12</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E12" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>465</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>484</v>
-      </c>
       <c r="G12" s="7" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C13" s="59" t="n">
         <f aca="false">SUM(C6:C12)</f>
-        <v>136.233333333333</v>
+        <v>161.233333333333</v>
       </c>
       <c r="D13" s="59" t="n">
         <f aca="false">SUM(D6:D12)</f>
-        <v>1634.8</v>
+        <v>1934.8</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C15" s="58" t="n">
         <v>29</v>
@@ -11850,21 +11839,21 @@
         <v>348</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F15" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="G15" s="7" t="s">
         <v>466</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C16" s="58" t="n">
         <v>99</v>
@@ -11874,21 +11863,21 @@
         <v>1188</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F16" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="G16" s="7" t="s">
         <v>466</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C17" s="58" t="n">
         <v>59</v>
@@ -11898,21 +11887,21 @@
         <v>708</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C18" s="58" t="n">
         <v>59</v>
@@ -11922,21 +11911,21 @@
         <v>708</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F18" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="G18" s="7" t="s">
         <v>466</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C19" s="18" t="n">
         <f aca="false">D19/12</f>
@@ -11946,18 +11935,18 @@
         <v>141</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C20" s="59" t="n">
         <f aca="false">SUM(C15:C19)</f>
@@ -11970,32 +11959,32 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C22" s="60" t="n">
         <f aca="false">C13+C20</f>
-        <v>393.983333333333</v>
+        <v>418.983333333333</v>
       </c>
       <c r="D22" s="60" t="n">
         <f aca="false">D13+D20</f>
-        <v>4727.8</v>
+        <v>5027.8</v>
       </c>
       <c r="G22" s="23" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="23" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C23" s="23"/>
       <c r="G23" s="51" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
@@ -12006,58 +11995,58 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B26" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="D26" s="9" t="s">
         <v>505</v>
       </c>
-      <c r="C26" s="9" t="s">
-        <v>506</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>507</v>
-      </c>
       <c r="E26" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B27" s="54" t="n">
         <v>40</v>
       </c>
       <c r="C27" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="E27" s="7" t="s">
         <v>509</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B28" s="54" t="n">
         <v>160</v>
       </c>
       <c r="C28" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="E28" s="7" t="s">
         <v>513</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>514</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -12068,81 +12057,81 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="C31" s="9" t="s">
         <v>517</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="D31" s="9" t="s">
         <v>518</v>
       </c>
-      <c r="C31" s="9" t="s">
-        <v>519</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>520</v>
-      </c>
       <c r="E31" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B32" s="58" t="n">
         <v>59</v>
       </c>
       <c r="C32" s="18" t="n">
         <f aca="false">$C$22-$C$17+B32</f>
-        <v>393.983333333333</v>
+        <v>418.983333333333</v>
       </c>
       <c r="D32" s="18" t="n">
         <f aca="false">C32-$C$22</f>
         <v>0</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B33" s="58" t="n">
         <v>0</v>
       </c>
       <c r="C33" s="18" t="n">
         <f aca="false">$C$22-$C$17+B33</f>
-        <v>334.983333333333</v>
+        <v>359.983333333333</v>
       </c>
       <c r="D33" s="18" t="n">
         <f aca="false">C33-$C$22</f>
         <v>-59</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B34" s="58" t="n">
         <v>159</v>
       </c>
       <c r="C34" s="18" t="n">
         <f aca="false">$C$22-$C$17+B34</f>
-        <v>493.983333333333</v>
+        <v>518.983333333333</v>
       </c>
       <c r="D34" s="18" t="n">
         <f aca="false">C34-$C$22</f>
         <v>100</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
@@ -12162,62 +12151,62 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="23" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C39" s="32" t="s">
+        <v>184</v>
+      </c>
+      <c r="D39" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="D39" s="32" t="s">
+      <c r="E39" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="E39" s="32" t="s">
+      <c r="F39" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="F39" s="32" t="s">
+      <c r="G39" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="G39" s="32" t="s">
+      <c r="H39" s="32" t="s">
         <v>189</v>
       </c>
-      <c r="H39" s="32" t="s">
+      <c r="I39" s="32" t="s">
         <v>190</v>
       </c>
-      <c r="I39" s="32" t="s">
+      <c r="J39" s="32" t="s">
         <v>191</v>
       </c>
-      <c r="J39" s="32" t="s">
+      <c r="K39" s="32" t="s">
         <v>192</v>
       </c>
-      <c r="K39" s="32" t="s">
+      <c r="L39" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="L39" s="32" t="s">
+      <c r="M39" s="32" t="s">
         <v>194</v>
       </c>
-      <c r="M39" s="32" t="s">
+      <c r="N39" s="32" t="s">
         <v>195</v>
       </c>
-      <c r="N39" s="32" t="s">
+      <c r="O39" s="32" t="s">
         <v>196</v>
-      </c>
-      <c r="O39" s="32" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C40" s="54" t="n">
         <v>0</v>
@@ -12262,10 +12251,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C41" s="54"/>
       <c r="D41" s="54"/>
@@ -12288,10 +12277,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C42" s="54"/>
       <c r="D42" s="54"/>
@@ -12314,10 +12303,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C43" s="54"/>
       <c r="D43" s="54"/>
@@ -12340,10 +12329,10 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C44" s="54"/>
       <c r="D44" s="54"/>
@@ -12357,19 +12346,19 @@
       <c r="L44" s="54"/>
       <c r="M44" s="54"/>
       <c r="N44" s="54" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="O44" s="59" t="n">
         <f aca="false">SUM(C44:N44)</f>
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="B45" s="23" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="54"/>
@@ -12383,19 +12372,19 @@
       <c r="L45" s="54"/>
       <c r="M45" s="54"/>
       <c r="N45" s="54" t="n">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="O45" s="59" t="n">
         <f aca="false">SUM(C45:N45)</f>
-        <v>99</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B46" s="23" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C46" s="54"/>
       <c r="D46" s="54"/>
@@ -12409,19 +12398,19 @@
       <c r="L46" s="54"/>
       <c r="M46" s="54"/>
       <c r="N46" s="54" t="n">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="O46" s="59" t="n">
         <f aca="false">SUM(C46:N46)</f>
-        <v>59</v>
+        <v>99</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C47" s="54"/>
       <c r="D47" s="54"/>
@@ -12444,10 +12433,10 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>533</v>
+        <v>493</v>
       </c>
       <c r="B48" s="23" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="C48" s="54"/>
       <c r="D48" s="54"/>
@@ -12461,19 +12450,19 @@
       <c r="L48" s="54"/>
       <c r="M48" s="54"/>
       <c r="N48" s="54" t="n">
-        <v>141</v>
+        <v>59</v>
       </c>
       <c r="O48" s="59" t="n">
         <f aca="false">SUM(C48:N48)</f>
-        <v>141</v>
+        <v>59</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="C49" s="54"/>
       <c r="D49" s="54"/>
@@ -12486,68 +12475,94 @@
       <c r="K49" s="54"/>
       <c r="L49" s="54"/>
       <c r="M49" s="54"/>
-      <c r="N49" s="54"/>
+      <c r="N49" s="54" t="n">
+        <v>141</v>
+      </c>
       <c r="O49" s="59" t="n">
         <f aca="false">SUM(C49:N49)</f>
-        <v>0</v>
+        <v>141</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="B50" s="23"/>
-      <c r="C50" s="59" t="n">
-        <f aca="false">SUM(C40:C49)</f>
-        <v>0</v>
-      </c>
-      <c r="D50" s="59" t="n">
-        <f aca="false">SUM(D40:D49)</f>
-        <v>0</v>
-      </c>
-      <c r="E50" s="59" t="n">
-        <f aca="false">SUM(E40:E49)</f>
-        <v>0</v>
-      </c>
-      <c r="F50" s="59" t="n">
-        <f aca="false">SUM(F40:F49)</f>
-        <v>0</v>
-      </c>
-      <c r="G50" s="59" t="n">
-        <f aca="false">SUM(G40:G49)</f>
-        <v>0</v>
-      </c>
-      <c r="H50" s="59" t="n">
-        <f aca="false">SUM(H40:H49)</f>
-        <v>0</v>
-      </c>
-      <c r="I50" s="59" t="n">
-        <f aca="false">SUM(I40:I49)</f>
-        <v>0</v>
-      </c>
-      <c r="J50" s="59" t="n">
-        <f aca="false">SUM(J40:J49)</f>
-        <v>0</v>
-      </c>
-      <c r="K50" s="59" t="n">
-        <f aca="false">SUM(K40:K49)</f>
-        <v>0</v>
-      </c>
-      <c r="L50" s="59" t="n">
-        <f aca="false">SUM(L40:L49)</f>
-        <v>0.19</v>
-      </c>
-      <c r="M50" s="59" t="n">
-        <f aca="false">SUM(M40:M49)</f>
-        <v>26.75</v>
-      </c>
-      <c r="N50" s="59" t="n">
-        <f aca="false">SUM(N40:N49)</f>
-        <v>519.9</v>
-      </c>
+        <v>533</v>
+      </c>
+      <c r="B50" s="23" t="s">
+        <v>534</v>
+      </c>
+      <c r="C50" s="54"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="54"/>
+      <c r="I50" s="54"/>
+      <c r="J50" s="54"/>
+      <c r="K50" s="54"/>
+      <c r="L50" s="54"/>
+      <c r="M50" s="54"/>
+      <c r="N50" s="54"/>
       <c r="O50" s="59" t="n">
         <f aca="false">SUM(C50:N50)</f>
-        <v>546.84</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B51" s="23"/>
+      <c r="C51" s="59" t="n">
+        <f aca="false">SUM(C40:C50)</f>
+        <v>0</v>
+      </c>
+      <c r="D51" s="59" t="n">
+        <f aca="false">SUM(D40:D50)</f>
+        <v>0</v>
+      </c>
+      <c r="E51" s="59" t="n">
+        <f aca="false">SUM(E40:E50)</f>
+        <v>0</v>
+      </c>
+      <c r="F51" s="59" t="n">
+        <f aca="false">SUM(F40:F50)</f>
+        <v>0</v>
+      </c>
+      <c r="G51" s="59" t="n">
+        <f aca="false">SUM(G40:G50)</f>
+        <v>0</v>
+      </c>
+      <c r="H51" s="59" t="n">
+        <f aca="false">SUM(H40:H50)</f>
+        <v>0</v>
+      </c>
+      <c r="I51" s="59" t="n">
+        <f aca="false">SUM(I40:I50)</f>
+        <v>0</v>
+      </c>
+      <c r="J51" s="59" t="n">
+        <f aca="false">SUM(J40:J50)</f>
+        <v>0</v>
+      </c>
+      <c r="K51" s="59" t="n">
+        <f aca="false">SUM(K40:K50)</f>
+        <v>0</v>
+      </c>
+      <c r="L51" s="59" t="n">
+        <f aca="false">SUM(L40:L50)</f>
+        <v>0.19</v>
+      </c>
+      <c r="M51" s="59" t="n">
+        <f aca="false">SUM(M40:M50)</f>
+        <v>26.75</v>
+      </c>
+      <c r="N51" s="59" t="n">
+        <f aca="false">SUM(N40:N50)</f>
+        <v>544.9</v>
+      </c>
+      <c r="O51" s="59" t="n">
+        <f aca="false">SUM(C51:N51)</f>
+        <v>571.84</v>
       </c>
     </row>
   </sheetData>
@@ -12586,7 +12601,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -12598,7 +12613,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -12610,29 +12625,29 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
       <c r="H4" s="9" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B5" s="61" t="n">
         <v>0</v>
@@ -12642,18 +12657,18 @@
         <v>4.1522369744</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B6" s="62" t="n">
         <v>0</v>
@@ -12663,18 +12678,18 @@
         <v>236.8317</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B7" s="63" t="n">
         <f aca="false">Expenses!C20</f>
@@ -12685,165 +12700,165 @@
         <v>5257.75</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B8" s="64" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C8" s="43" t="n">
         <f aca="false">Calculator!B64</f>
         <v>1266.24516674166</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>547</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>548</v>
+      </c>
+      <c r="H8" s="7" t="s">
         <v>549</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>550</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B9" s="64" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C9" s="65" t="n">
         <f aca="false">Calculator!B52</f>
         <v>0.85</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B10" s="64" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C10" s="65" t="n">
         <f aca="false">Calculator!B50</f>
         <v>0.05</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C11" s="43" t="n">
         <f aca="false">Calculator!B67</f>
         <v>4026.1389</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B12" s="64" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C12" s="66" t="n">
         <f aca="false">Calculator!B68</f>
         <v>3.17958876033477</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B13" s="64" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C13" s="57" t="n">
         <f aca="false">Calculator!B69</f>
         <v>6.29012161871344</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B14" s="64" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C14" s="43" t="n">
         <f aca="false">Calculator!B70</f>
         <v>19667.6268290002</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>
